--- a/《移动应用开发技术》技术点对应.xlsx
+++ b/《移动应用开发技术》技术点对应.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
   <si>
     <t>《移动应用开发技术》技术点对应</t>
   </si>
@@ -128,16 +128,34 @@
     <t>实验2</t>
   </si>
   <si>
+    <t>4个Fragment（Game/Help/Settings/Ranking）+ BottomNavigationView + Navigation Component 完整实现</t>
+  </si>
+  <si>
     <t>选项菜单</t>
   </si>
   <si>
+    <t>main_options_menu.xml + onCreateOptionsMenu/onOptionsItemSelected 实现，难度设置跳转SettingsFragment</t>
+  </si>
+  <si>
     <t>上下文菜单</t>
   </si>
   <si>
+    <t>board_context_menu.xml + registerForContextMenu + onContextItemSelected 实现打乱/重开/暂停</t>
+  </si>
+  <si>
     <t>难度选择</t>
   </si>
   <si>
+    <t>SettingsFragment RadioGroup 三档难度 + PreferenceUtil 持久化 + GameFragment 动态调整参数</t>
+  </si>
+  <si>
     <t>intent</t>
+  </si>
+  <si>
+    <t>GameResultActivity 接收Intent显示结果、VersionCheckActivity 跳转演示，数据传递完整</t>
+  </si>
+  <si>
+    <t>Service(MusicService)、BroadcastReceiver(Headset/GameResult)、ContentProvider(RankProvider)、SQLite、ObjectAnimator动画、RecyclerView/CursorAdapter</t>
   </si>
   <si>
     <t>实验3</t>
@@ -1932,7 +1950,7 @@
       <c r="N13"/>
       <c r="O13"/>
     </row>
-    <row r="14" ht="19" spans="1:15">
+    <row r="14" ht="89" spans="1:15">
       <c r="A14" s="30" t="s">
         <v>30</v>
       </c>
@@ -1945,7 +1963,9 @@
       <c r="D14" s="31">
         <v>10</v>
       </c>
-      <c r="E14" s="32"/>
+      <c r="E14" s="32" t="s">
+        <v>31</v>
+      </c>
       <c r="F14" s="33"/>
       <c r="G14" s="33"/>
       <c r="H14" s="34"/>
@@ -1957,18 +1977,20 @@
       <c r="N14"/>
       <c r="O14"/>
     </row>
-    <row r="15" ht="19" spans="1:15">
+    <row r="15" ht="71.5" spans="1:15">
       <c r="A15" s="30"/>
       <c r="B15" s="23">
         <v>2</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D15" s="35">
         <v>20</v>
       </c>
-      <c r="E15" s="36"/>
+      <c r="E15" s="36" t="s">
+        <v>33</v>
+      </c>
       <c r="F15" s="37"/>
       <c r="G15" s="37"/>
       <c r="H15" s="38"/>
@@ -1980,18 +2002,20 @@
       <c r="N15"/>
       <c r="O15"/>
     </row>
-    <row r="16" ht="19" spans="1:15">
+    <row r="16" ht="71.5" spans="1:15">
       <c r="A16" s="30"/>
       <c r="B16" s="23">
         <v>3</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" s="35">
         <v>20</v>
       </c>
-      <c r="E16" s="36"/>
+      <c r="E16" s="36" t="s">
+        <v>35</v>
+      </c>
       <c r="F16" s="37"/>
       <c r="G16" s="37"/>
       <c r="H16" s="38"/>
@@ -2003,18 +2027,20 @@
       <c r="N16"/>
       <c r="O16"/>
     </row>
-    <row r="17" ht="19" spans="1:15">
+    <row r="17" ht="54" spans="1:15">
       <c r="A17" s="30"/>
       <c r="B17" s="23">
         <v>4</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D17" s="35">
         <v>20</v>
       </c>
-      <c r="E17" s="36"/>
+      <c r="E17" s="36" t="s">
+        <v>37</v>
+      </c>
       <c r="F17" s="37"/>
       <c r="G17" s="37"/>
       <c r="H17" s="38"/>
@@ -2026,18 +2052,20 @@
       <c r="N17"/>
       <c r="O17"/>
     </row>
-    <row r="18" ht="19" spans="1:15">
+    <row r="18" ht="54" spans="1:15">
       <c r="A18" s="30"/>
       <c r="B18" s="23">
         <v>5</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D18" s="35">
         <v>20</v>
       </c>
-      <c r="E18" s="36"/>
+      <c r="E18" s="36" t="s">
+        <v>39</v>
+      </c>
       <c r="F18" s="37"/>
       <c r="G18" s="37"/>
       <c r="H18" s="38"/>
@@ -2049,7 +2077,7 @@
       <c r="N18"/>
       <c r="O18"/>
     </row>
-    <row r="19" ht="19" spans="1:15">
+    <row r="19" ht="106.5" spans="1:15">
       <c r="A19" s="30"/>
       <c r="B19" s="23">
         <v>6</v>
@@ -2060,7 +2088,9 @@
       <c r="D19" s="35">
         <v>10</v>
       </c>
-      <c r="E19" s="36"/>
+      <c r="E19" s="36" t="s">
+        <v>40</v>
+      </c>
       <c r="F19" s="37"/>
       <c r="G19" s="37"/>
       <c r="H19" s="38"/>
@@ -2158,13 +2188,13 @@
     </row>
     <row r="24" ht="19" spans="1:15">
       <c r="A24" s="30" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B24" s="23">
         <v>1</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D24" s="35">
         <v>20</v>
@@ -2187,7 +2217,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D25" s="35">
         <v>20</v>
@@ -2210,7 +2240,7 @@
         <v>3</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D26" s="35">
         <v>20</v>
@@ -2233,7 +2263,7 @@
         <v>4</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D27" s="35">
         <v>20</v>
@@ -2256,7 +2286,7 @@
         <v>5</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D28" s="35">
         <v>10</v>
@@ -2382,13 +2412,13 @@
     </row>
     <row r="34" ht="19" spans="1:15">
       <c r="A34" s="30" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B34" s="23">
         <v>1</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D34" s="35">
         <v>40</v>
@@ -2411,7 +2441,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D35" s="35">
         <v>30</v>
@@ -2428,7 +2458,7 @@
         <v>3</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D36" s="35">
         <v>20</v>

--- a/《移动应用开发技术》技术点对应.xlsx
+++ b/《移动应用开发技术》技术点对应.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
   <si>
     <t>《移动应用开发技术》技术点对应</t>
   </si>
@@ -164,6 +164,9 @@
     <t>音效</t>
   </si>
   <si>
+    <t>实现完成</t>
+  </si>
+  <si>
     <t>service</t>
   </si>
   <si>
@@ -174,6 +177,9 @@
   </si>
   <si>
     <t>broadcast</t>
+  </si>
+  <si>
+    <t>中英文切换</t>
   </si>
   <si>
     <t>实验4</t>
@@ -1966,7 +1972,9 @@
       <c r="E14" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="33"/>
+      <c r="F14" s="33">
+        <v>100</v>
+      </c>
       <c r="G14" s="33"/>
       <c r="H14" s="34"/>
       <c r="I14" s="46"/>
@@ -1991,7 +1999,9 @@
       <c r="E15" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="37"/>
+      <c r="F15" s="37">
+        <v>100</v>
+      </c>
       <c r="G15" s="37"/>
       <c r="H15" s="38"/>
       <c r="I15" s="47"/>
@@ -2016,7 +2026,9 @@
       <c r="E16" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="37"/>
+      <c r="F16" s="37">
+        <v>100</v>
+      </c>
       <c r="G16" s="37"/>
       <c r="H16" s="38"/>
       <c r="I16" s="47"/>
@@ -2041,7 +2053,9 @@
       <c r="E17" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="37"/>
+      <c r="F17" s="37">
+        <v>100</v>
+      </c>
       <c r="G17" s="37"/>
       <c r="H17" s="38"/>
       <c r="I17" s="47"/>
@@ -2066,7 +2080,9 @@
       <c r="E18" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="37"/>
+      <c r="F18" s="37">
+        <v>100</v>
+      </c>
       <c r="G18" s="37"/>
       <c r="H18" s="38"/>
       <c r="I18" s="47"/>
@@ -2091,7 +2107,9 @@
       <c r="E19" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="37"/>
+      <c r="F19" s="37">
+        <v>100</v>
+      </c>
       <c r="G19" s="37"/>
       <c r="H19" s="38"/>
       <c r="I19" s="47"/>
@@ -2199,8 +2217,12 @@
       <c r="D24" s="35">
         <v>20</v>
       </c>
-      <c r="E24" s="24"/>
-      <c r="F24" s="25"/>
+      <c r="E24" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="25">
+        <v>100</v>
+      </c>
       <c r="G24" s="25"/>
       <c r="H24" s="26"/>
       <c r="I24" s="44"/>
@@ -2217,13 +2239,17 @@
         <v>2</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D25" s="35">
         <v>20</v>
       </c>
-      <c r="E25" s="24"/>
-      <c r="F25" s="25"/>
+      <c r="E25" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="25">
+        <v>100</v>
+      </c>
       <c r="G25" s="25"/>
       <c r="H25" s="26"/>
       <c r="I25" s="44"/>
@@ -2240,13 +2266,17 @@
         <v>3</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D26" s="35">
         <v>20</v>
       </c>
-      <c r="E26" s="24"/>
-      <c r="F26" s="25"/>
+      <c r="E26" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="25">
+        <v>100</v>
+      </c>
       <c r="G26" s="25"/>
       <c r="H26" s="26"/>
       <c r="I26" s="44"/>
@@ -2263,13 +2293,17 @@
         <v>4</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D27" s="35">
         <v>20</v>
       </c>
-      <c r="E27" s="24"/>
-      <c r="F27" s="25"/>
+      <c r="E27" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="25">
+        <v>100</v>
+      </c>
       <c r="G27" s="25"/>
       <c r="H27" s="26"/>
       <c r="I27" s="44"/>
@@ -2286,13 +2320,17 @@
         <v>5</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D28" s="35">
         <v>10</v>
       </c>
-      <c r="E28" s="24"/>
-      <c r="F28" s="25"/>
+      <c r="E28" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="25">
+        <v>100</v>
+      </c>
       <c r="G28" s="25"/>
       <c r="H28" s="26"/>
       <c r="I28" s="44"/>
@@ -2314,8 +2352,12 @@
       <c r="D29" s="35">
         <v>10</v>
       </c>
-      <c r="E29" s="24"/>
-      <c r="F29" s="25"/>
+      <c r="E29" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="25">
+        <v>100</v>
+      </c>
       <c r="G29" s="25"/>
       <c r="H29" s="26"/>
       <c r="I29" s="44"/>
@@ -2412,13 +2454,13 @@
     </row>
     <row r="34" ht="19" spans="1:15">
       <c r="A34" s="30" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B34" s="23">
         <v>1</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D34" s="35">
         <v>40</v>
@@ -2441,7 +2483,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D35" s="35">
         <v>30</v>
@@ -2458,7 +2500,7 @@
         <v>3</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D36" s="35">
         <v>20</v>
